--- a/conception/todo-echotranscribe.xlsx
+++ b/conception/todo-echotranscribe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ITU\S6\Soutenance\Projet de stage\EchoTranscribe\conception\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433B6DA8-E695-4DAA-A976-DE3FF4D20599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EAD653-36D7-4F09-B41E-D4AE885ADBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,40 @@
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Cedric Ced</author>
+  </authors>
+  <commentList>
+    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{39E79890-AAA9-4974-BE97-A0E3A621937C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Cedric Ced:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -636,7 +670,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -698,8 +732,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -718,6 +765,18 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -732,7 +791,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -744,6 +803,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -965,7 +1027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -980,27 +1042,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
@@ -1031,7 +1093,7 @@
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
@@ -1046,7 +1108,7 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
@@ -1106,159 +1168,159 @@
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="A12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="A13" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="A14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="A16" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="A18" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="A19" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="7" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1276,7 +1338,7 @@
         <v>150</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
@@ -3447,5 +3509,6 @@
     <hyperlink ref="D115" r:id="rId6" display="Home.vue" xr:uid="{BE2E178E-3E35-4F22-A5CC-D3A3FA5D8291}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId7"/>
 </worksheet>
 </file>